--- a/operatorslogin_excels/Manoj_Login_details.xlsx
+++ b/operatorslogin_excels/Manoj_Login_details.xlsx
@@ -409,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>manojchandran444@gmail.com</v>
+        <v>nubiznezakr@gmail.com</v>
       </c>
       <c r="B2" t="str">
         <v>8190098951</v>

--- a/operatorslogin_excels/Manoj_Login_details.xlsx
+++ b/operatorslogin_excels/Manoj_Login_details.xlsx
@@ -409,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>nubiznezakr@gmail.com</v>
+        <v>manojchandran444@gmail.com</v>
       </c>
       <c r="B2" t="str">
         <v>8190098951</v>
